--- a/VerveStacks_VNM_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_VNM_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFEA3855-A14C-48EC-9C8A-C5E15E4A9176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDC760B1-C4B7-4182-8CC8-B7F300126DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -805,13 +805,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S04aH03,S01aH03,S01aH02,S03aH03,S02aH03,S04aH02,S03aH02</t>
+    <t>S02aH03,S03aH03,S01aH03,S04aH03,S03aH02,S02aH02,S04aH02,S01aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S02aH01,S01aH01,S04aH01</t>
+    <t>S01aH01,S04aH01,S02aH01,S03aH01</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -958,10 +958,10 @@
     <t>S08aH06</t>
   </si>
   <si>
-    <t>S04aH03,S07aH04,S08aH03,S02aH02,S03aH04,S08aH05,S01aH02,S04aH04,S01aH03,S05aH02,S05aH03,S02aH03,S07aH03,S08aH02,S01aH05,S06aH05,S04aH02,S03aH05,S05aH05,S06aH04,S08aH04,S04aH05,S03aH03,S03aH02,S07aH05,S02aH04,S02aH05,S01aH04,S07aH02,S05aH04,S06aH02,S06aH03</t>
+    <t>S04aH03,S07aH04,S08aH03,S05aH04,S06aH02,S06aH03,S03aH04,S08aH05,S02aH03,S07aH03,S03aH02,S07aH05,S01aH02,S04aH04,S02aH04,S02aH05,S01aH04,S07aH02,S04aH02,S02aH02,S01aH03,S05aH02,S05aH03,S08aH02,S04aH05,S03aH05,S05aH05,S06aH04,S08aH04,S03aH03,S01aH05,S06aH05</t>
   </si>
   <si>
-    <t>S02aH01,S05aH06,S03aH01,S05aH01,S07aH06,S01aH05,S03aH06,S06aH05,S01aH01,S04aH01,S04aH06,S04aH05,S06aH01,S07aH05,S02aH05,S06aH06,S02aH06,S03aH05,S05aH05,S08aH01,S08aH05,S01aH06,S07aH01,S08aH06</t>
+    <t>S02aH01,S05aH06,S01aH06,S07aH01,S08aH06,S05aH01,S07aH06,S01aH01,S04aH01,S04aH06,S01aH05,S03aH06,S06aH05,S02aH06,S03aH05,S05aH05,S08aH01,S08aH05,S07aH05,S03aH01,S04aH05,S06aH01,S02aH05,S06aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1027,10 +1027,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaP,FaD,WaD,FaP,SaP,SaD,RaD,RaP</t>
+    <t>WaD,RaP,RaD,FaD,WaP,SaD,FaP,SaP</t>
   </si>
   <si>
-    <t>SaN,WaN,RaN,RaP,FaN,FaP,SaP,WaP</t>
+    <t>SaN,WaN,RaP,RaN,FaP,SaP,FaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24734,7 +24734,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BFD1387-234D-49F9-B055-9853BAEA3F5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BED7F6AC-94D9-480F-B7A9-3B32C35A0516}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25624,7 +25624,7 @@
         <v>152</v>
       </c>
       <c r="AM19">
-        <v>0.48080325254442563</v>
+        <v>0.48080325254442569</v>
       </c>
       <c r="AN19" t="s">
         <v>247</v>
@@ -25923,7 +25923,7 @@
         <v>152</v>
       </c>
       <c r="AM23">
-        <v>0.37782500000000002</v>
+        <v>0.37782499999999997</v>
       </c>
       <c r="AN23" t="s">
         <v>247</v>
@@ -27422,7 +27422,7 @@
         <v>152</v>
       </c>
       <c r="AM51">
-        <v>0.32756249999999998</v>
+        <v>0.32756250000000003</v>
       </c>
       <c r="AN51" t="s">
         <v>247</v>
@@ -28422,7 +28422,7 @@
         <v>152</v>
       </c>
       <c r="AM71">
-        <v>0.38246249999999998</v>
+        <v>0.38246249999999993</v>
       </c>
       <c r="AN71" t="s">
         <v>247</v>
@@ -29222,7 +29222,7 @@
         <v>152</v>
       </c>
       <c r="AM87">
-        <v>0.3838125</v>
+        <v>0.38381249999999995</v>
       </c>
       <c r="AN87" t="s">
         <v>247</v>
@@ -29422,7 +29422,7 @@
         <v>152</v>
       </c>
       <c r="AM91">
-        <v>0.38162499999999999</v>
+        <v>0.38162499999999994</v>
       </c>
       <c r="AN91" t="s">
         <v>247</v>
@@ -29622,7 +29622,7 @@
         <v>152</v>
       </c>
       <c r="AM95">
-        <v>0.3692375</v>
+        <v>0.36923749999999994</v>
       </c>
       <c r="AN95" t="s">
         <v>247</v>
@@ -30022,7 +30022,7 @@
         <v>152</v>
       </c>
       <c r="AM103">
-        <v>0.37230000000000002</v>
+        <v>0.37229999999999996</v>
       </c>
       <c r="AN103" t="s">
         <v>247</v>
@@ -30622,7 +30622,7 @@
         <v>152</v>
       </c>
       <c r="AM115">
-        <v>0.3717625</v>
+        <v>0.37176250000000005</v>
       </c>
       <c r="AN115" t="s">
         <v>247</v>
@@ -36424,7 +36424,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A0F8035-20DA-435B-A512-9BD30BAAD0A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{688779DC-CFDE-46AA-976E-F30CFFF81E24}">
   <dimension ref="A9:AN1162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39904,7 +39904,7 @@
         <v>152</v>
       </c>
       <c r="AM51">
-        <v>0.27327500000000005</v>
+        <v>0.27327499999999999</v>
       </c>
       <c r="AN51" t="s">
         <v>247</v>
@@ -40995,7 +40995,7 @@
         <v>152</v>
       </c>
       <c r="AM67">
-        <v>0.29725000000000001</v>
+        <v>0.29724999999999996</v>
       </c>
       <c r="AN67" t="s">
         <v>247</v>
@@ -44546,7 +44546,7 @@
         <v>152</v>
       </c>
       <c r="AM131">
-        <v>0.30814999999999998</v>
+        <v>0.30815000000000003</v>
       </c>
       <c r="AN131" t="s">
         <v>247</v>
@@ -45346,7 +45346,7 @@
         <v>152</v>
       </c>
       <c r="AM147">
-        <v>0.24042499999999997</v>
+        <v>0.240425</v>
       </c>
       <c r="AN147" t="s">
         <v>247</v>
@@ -45746,7 +45746,7 @@
         <v>152</v>
       </c>
       <c r="AM155">
-        <v>0.29127500000000001</v>
+        <v>0.29127499999999995</v>
       </c>
       <c r="AN155" t="s">
         <v>247</v>
@@ -46546,7 +46546,7 @@
         <v>152</v>
       </c>
       <c r="AM171">
-        <v>0.29610000000000003</v>
+        <v>0.29609999999999997</v>
       </c>
       <c r="AN171" t="s">
         <v>247</v>
@@ -79884,7 +79884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D25BB736-18CA-4A5F-B8BC-E8BBD974D6D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CF5F8A3-5D97-4F68-99D9-65BE4C767316}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -80113,7 +80113,7 @@
         <v>294</v>
       </c>
       <c r="AM11">
-        <v>0.41552740089091461</v>
+        <v>0.4155274008909145</v>
       </c>
       <c r="AN11" t="s">
         <v>247</v>
@@ -80222,7 +80222,7 @@
         <v>294</v>
       </c>
       <c r="AM13">
-        <v>0.51807842998889353</v>
+        <v>0.51807842998889342</v>
       </c>
       <c r="AN13" t="s">
         <v>247</v>
@@ -80272,7 +80272,7 @@
         <v>294</v>
       </c>
       <c r="AM14">
-        <v>0.42825833333333335</v>
+        <v>0.42825833333333324</v>
       </c>
       <c r="AN14" t="s">
         <v>247</v>
@@ -80322,7 +80322,7 @@
         <v>294</v>
       </c>
       <c r="AM15">
-        <v>0.44092499999999996</v>
+        <v>0.44092500000000007</v>
       </c>
       <c r="AN15" t="s">
         <v>247</v>
@@ -80422,7 +80422,7 @@
         <v>294</v>
       </c>
       <c r="AM17">
-        <v>0.43855833333333333</v>
+        <v>0.43855833333333322</v>
       </c>
       <c r="AN17" t="s">
         <v>247</v>
@@ -80472,7 +80472,7 @@
         <v>294</v>
       </c>
       <c r="AM18">
-        <v>0.43674166666666675</v>
+        <v>0.43674166666666664</v>
       </c>
       <c r="AN18" t="s">
         <v>247</v>
@@ -80522,7 +80522,7 @@
         <v>294</v>
       </c>
       <c r="AM19">
-        <v>0.44109166666666666</v>
+        <v>0.44109166666666672</v>
       </c>
       <c r="AN19" t="s">
         <v>247</v>
@@ -80722,7 +80722,7 @@
         <v>294</v>
       </c>
       <c r="AM23">
-        <v>0.36294166666666666</v>
+        <v>0.36294166666666672</v>
       </c>
       <c r="AN23" t="s">
         <v>247</v>
@@ -80772,7 +80772,7 @@
         <v>294</v>
       </c>
       <c r="AM24">
-        <v>0.42940000000000006</v>
+        <v>0.4294</v>
       </c>
       <c r="AN24" t="s">
         <v>247</v>
@@ -80822,7 +80822,7 @@
         <v>294</v>
       </c>
       <c r="AM25">
-        <v>0.43345833333333328</v>
+        <v>0.43345833333333333</v>
       </c>
       <c r="AN25" t="s">
         <v>247</v>
@@ -80872,7 +80872,7 @@
         <v>294</v>
       </c>
       <c r="AM26">
-        <v>0.42721666666666663</v>
+        <v>0.42721666666666658</v>
       </c>
       <c r="AN26" t="s">
         <v>247</v>
@@ -80998,7 +80998,7 @@
         <v>294</v>
       </c>
       <c r="AM29">
-        <v>0.43145833333333333</v>
+        <v>0.43145833333333328</v>
       </c>
       <c r="AN29" t="s">
         <v>247</v>
@@ -81036,7 +81036,7 @@
         <v>294</v>
       </c>
       <c r="AM30">
-        <v>0.43819166666666659</v>
+        <v>0.4381916666666667</v>
       </c>
       <c r="AN30" t="s">
         <v>247</v>
@@ -81074,7 +81074,7 @@
         <v>294</v>
       </c>
       <c r="AM31">
-        <v>0.42312500000000003</v>
+        <v>0.42312499999999997</v>
       </c>
       <c r="AN31" t="s">
         <v>247</v>
@@ -81112,7 +81112,7 @@
         <v>294</v>
       </c>
       <c r="AM32">
-        <v>0.432475</v>
+        <v>0.43247499999999994</v>
       </c>
       <c r="AN32" t="s">
         <v>247</v>
@@ -81138,7 +81138,7 @@
         <v>294</v>
       </c>
       <c r="AM33">
-        <v>0.43867500000000009</v>
+        <v>0.43867499999999998</v>
       </c>
       <c r="AN33" t="s">
         <v>247</v>
@@ -81164,7 +81164,7 @@
         <v>294</v>
       </c>
       <c r="AM34">
-        <v>0.42349999999999999</v>
+        <v>0.42350000000000004</v>
       </c>
       <c r="AN34" t="s">
         <v>247</v>
@@ -81178,7 +81178,7 @@
         <v>294</v>
       </c>
       <c r="AM35">
-        <v>0.43248333333333328</v>
+        <v>0.43248333333333333</v>
       </c>
       <c r="AN35" t="s">
         <v>247</v>
@@ -81220,7 +81220,7 @@
         <v>294</v>
       </c>
       <c r="AM38">
-        <v>0.41879999999999989</v>
+        <v>0.41880000000000006</v>
       </c>
       <c r="AN38" t="s">
         <v>247</v>
@@ -81246,7 +81246,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30CAC0C-C3E3-46CC-925C-E3BCC504BF5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC39325-613B-4F87-987C-A82B2D2F6521}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -82435,7 +82435,7 @@
         <v>297</v>
       </c>
       <c r="AM23">
-        <v>0.53883333333333328</v>
+        <v>0.53883333333333339</v>
       </c>
       <c r="AN23" t="s">
         <v>247</v>
@@ -83684,7 +83684,7 @@
         <v>302</v>
       </c>
       <c r="AM46">
-        <v>0.37736666666666663</v>
+        <v>0.37736666666666668</v>
       </c>
       <c r="AN46" t="s">
         <v>247</v>
@@ -84684,7 +84684,7 @@
         <v>302</v>
       </c>
       <c r="AM66">
-        <v>0.36536666666666662</v>
+        <v>0.36536666666666667</v>
       </c>
       <c r="AN66" t="s">
         <v>247</v>
@@ -85284,7 +85284,7 @@
         <v>302</v>
       </c>
       <c r="AM78">
-        <v>0.31146666666666667</v>
+        <v>0.31146666666666661</v>
       </c>
       <c r="AN78" t="s">
         <v>247</v>
@@ -85384,7 +85384,7 @@
         <v>299</v>
       </c>
       <c r="AM80">
-        <v>0.26449999999999996</v>
+        <v>0.26450000000000001</v>
       </c>
       <c r="AN80" t="s">
         <v>247</v>
@@ -85584,7 +85584,7 @@
         <v>299</v>
       </c>
       <c r="AM84">
-        <v>0.31153333333333333</v>
+        <v>0.31153333333333327</v>
       </c>
       <c r="AN84" t="s">
         <v>247</v>
@@ -86084,7 +86084,7 @@
         <v>302</v>
       </c>
       <c r="AM94">
-        <v>0.3801666666666666</v>
+        <v>0.38016666666666671</v>
       </c>
       <c r="AN94" t="s">
         <v>247</v>
@@ -86334,7 +86334,7 @@
         <v>297</v>
       </c>
       <c r="AM99">
-        <v>0.55223333333333346</v>
+        <v>0.55223333333333335</v>
       </c>
       <c r="AN99" t="s">
         <v>247</v>
@@ -87084,7 +87084,7 @@
         <v>302</v>
       </c>
       <c r="AM114">
-        <v>0.35660000000000003</v>
+        <v>0.35659999999999997</v>
       </c>
       <c r="AN114" t="s">
         <v>247</v>
@@ -87484,7 +87484,7 @@
         <v>302</v>
       </c>
       <c r="AM122">
-        <v>0.34856666666666669</v>
+        <v>0.34856666666666664</v>
       </c>
       <c r="AN122" t="s">
         <v>247</v>
